--- a/docs/arb_stiffness_old.xlsx
+++ b/docs/arb_stiffness_old.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Parameters" sheetId="5" r:id="rId2"/>
     <sheet name="Samples" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1" calcMode="auto"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -223,13 +223,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="10">
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
     <numFmt numFmtId="178" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000000"/>
+    <numFmt numFmtId="180" formatCode="0.0"/>
+    <numFmt numFmtId="181" formatCode="0.0000"/>
+    <numFmt numFmtId="182" formatCode="0.000"/>
+    <numFmt numFmtId="183" formatCode="0.000000"/>
+    <numFmt numFmtId="184" formatCode="0"/>
+    <numFmt numFmtId="185" formatCode="0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -302,8 +308,113 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,8 +446,80 @@
         <fgColor rgb="FFEDF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -354,10 +537,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -432,6 +616,159 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="1"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="17" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="17" fillId="12" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="12" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="26" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="26" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="22" fillId="16" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="22" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="26" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="22" fillId="16" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="22" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="16" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -517,16 +854,16 @@
             <c:numRef>
               <c:f>Samples!$C$15:$C$17</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.0038661085437566</c:v>
+                  <c:v>4.003866108543757</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.4551008893647595</c:v>
+                  <c:v>8.45510088936476</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.562650598490066</c:v>
+                  <c:v>15.56265059849007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -570,16 +907,16 @@
             <c:numRef>
               <c:f>Samples!$D$15:$D$17</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>10.924292019930764</c:v>
+                  <c:v>11.112357594531261</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.4667453290695</c:v>
+                  <c:v>22.853518344840758</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.835749148329093</c:v>
+                  <c:v>38.48710503400469</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,16 +1131,16 @@
             <c:numRef>
               <c:f>Samples!$C$22:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.8029556626481638</c:v>
+                  <c:v>4.802955662648164</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10.142565608820032</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18.6686364607279</c:v>
+                  <c:v>18.668636460727903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -847,10 +1184,10 @@
             <c:numRef>
               <c:f>Samples!$D$22:$D$24</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12.824173715651447</c:v>
+                  <c:v>12.824173715651444</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>26.374015304573856</c:v>
@@ -2242,1122 +2579,1187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF31475E"/>
-  </sheetPr>
-  <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="2.75" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="8" width="16.25" customWidth="1"/>
-    <col min="9" max="9" width="2.75" customWidth="1"/>
-    <col min="10" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="10.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="39.950000000000003" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="6">
-        <v>14.6</v>
-      </c>
-      <c r="E7" s="8">
-        <f>$E$8*(D7/$D$8)^4</f>
-        <v>941.40636852684645</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1988</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6">
-        <v>20.5</v>
-      </c>
-      <c r="E9" s="8">
-        <f>$E$8*(D9/$D$8)^4</f>
-        <v>3659.1579207191098</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6">
-        <v>16.2</v>
-      </c>
-      <c r="E10" s="9">
-        <f>$E$11*(D10/$D$11)^4</f>
-        <v>1429.0674406245323</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="6">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2939</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="6">
-        <v>22.1</v>
-      </c>
-      <c r="E12" s="9">
-        <f>$E$11*(D12/$D$11)^4</f>
-        <v>4949.5049290944507</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A17" s="2"/>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="10">
-        <v>167</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="39.950000000000003" customHeight="1">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="11">
-        <v>-1.0609999999999999</v>
-      </c>
-      <c r="D20" s="11">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="E20" s="11">
-        <v>-0.89900000000000002</v>
-      </c>
-      <c r="F20" s="11">
-        <v>0.185</v>
-      </c>
-      <c r="G20" s="12">
-        <f>IF(COUNT(C20:F20)&lt;4,"",IF(H20=0,"无效半径",IF(D20&lt;F20,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E20-C20)*1000/H20))))))</f>
-        <v>3.5322945838909319</v>
-      </c>
-      <c r="H20" s="14">
-        <f>IF(COUNT(C20:F20)&lt;4,"",1000*SQRT((C20-E20)^2+(D20-F20)^2))</f>
-        <v>162.30834852218777</v>
-      </c>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A21" s="2"/>
-      <c r="B21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="11">
-        <v>-1.046</v>
-      </c>
-      <c r="D21" s="11">
-        <v>0.254</v>
-      </c>
-      <c r="E21" s="11">
-        <v>-0.89900000000000002</v>
-      </c>
-      <c r="F21" s="11">
-        <v>0.185</v>
-      </c>
-      <c r="G21" s="13">
-        <f>IF(COUNT(C21:F21)&lt;4,"",IF(H21=0,"无效半径",IF(D21&lt;F21,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E21-C21)*1000/H21))))))</f>
-        <v>25.144785630678921</v>
-      </c>
-      <c r="H21" s="15">
-        <f>IF(COUNT(C21:F21)&lt;4,"",1000*SQRT((C21-E21)^2+(D21-F21)^2))</f>
-        <v>162.3884232326923</v>
-      </c>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A24" s="2"/>
-      <c r="B24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="10">
-        <v>166</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" ht="39.950000000000003" customHeight="1">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A27" s="2"/>
-      <c r="B27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="11">
-        <v>1.321</v>
-      </c>
-      <c r="D27" s="11">
-        <v>0.186</v>
-      </c>
-      <c r="E27" s="11">
-        <v>1.4550000000000001</v>
-      </c>
-      <c r="F27" s="11">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="G27" s="13">
-        <f>IF(COUNT(C27:F27)&lt;4,"",IF(H27=0,"无效半径",IF(D27&lt;F27,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E27-C27)*1000/H27))))))</f>
-        <v>-29.235804568699994</v>
-      </c>
-      <c r="H27" s="15">
-        <f>IF(COUNT(C27:F27)&lt;4,"",1000*SQRT((C27-E27)^2+(D27-F27)^2))</f>
-        <v>153.5610627730872</v>
-      </c>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A28" s="2"/>
-      <c r="B28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="11">
-        <v>1.3009999999999999</v>
-      </c>
-      <c r="D28" s="11">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="E28" s="11">
-        <v>1.4550000000000001</v>
-      </c>
-      <c r="F28" s="11">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="G28" s="12">
-        <f>IF(COUNT(C28:F28)&lt;4,"",IF(H28=0,"无效半径",IF(D28&lt;F28,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E28-C28)*1000/H28))))))</f>
-        <v>-0.74405920288851057</v>
-      </c>
-      <c r="H28" s="14">
-        <f>IF(COUNT(C28:F28)&lt;4,"",1000*SQRT((C28-E28)^2+(D28-F28)^2))</f>
-        <v>154.01298646542779</v>
-      </c>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A31" s="2"/>
-      <c r="B31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="10">
-        <v>266</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9" ht="39.950000000000003" customHeight="1">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A34" s="2"/>
-      <c r="B34" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="11">
-        <v>-1.0609999999999999</v>
-      </c>
-      <c r="D34" s="11">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="E34" s="11">
-        <v>-0.89900000000000002</v>
-      </c>
-      <c r="F34" s="11">
-        <v>0.185</v>
-      </c>
-      <c r="G34" s="12">
-        <f>IF(COUNT(C34:F34)&lt;4,"",IF(H34=0,"无效半径",IF(D34&lt;F34,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E34-C34)*1000/H34))))))</f>
-        <v>3.5322945838909319</v>
-      </c>
-      <c r="H34" s="14">
-        <f>IF(COUNT(C34:F34)&lt;4,"",1000*SQRT((C34-E34)^2+(D34-F34)^2))</f>
-        <v>162.30834852218777</v>
-      </c>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="11">
-        <v>-1.032</v>
-      </c>
-      <c r="D35" s="11">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="E35" s="11">
-        <v>-0.89900000000000002</v>
-      </c>
-      <c r="F35" s="11">
-        <v>0.185</v>
-      </c>
-      <c r="G35" s="13">
-        <f>IF(COUNT(C35:F35)&lt;4,"",IF(H35=0,"无效半径",IF(D35&lt;F35,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E35-C35)*1000/H35))))))</f>
-        <v>34.963097546036515</v>
-      </c>
-      <c r="H35" s="15">
-        <f>IF(COUNT(C35:F35)&lt;4,"",1000*SQRT((C35-E35)^2+(D35-F35)^2))</f>
-        <v>162.28986413205234</v>
-      </c>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A38" s="2"/>
-      <c r="B38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="10">
-        <v>268</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="G39" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9" ht="39.950000000000003" customHeight="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" s="11">
-        <v>1.321</v>
-      </c>
-      <c r="D41" s="11">
-        <v>0.186</v>
-      </c>
-      <c r="E41" s="11">
-        <v>1.4550000000000001</v>
-      </c>
-      <c r="F41" s="11">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="G41" s="13">
-        <f>IF(COUNT(C41:F41)&lt;4,"",IF(H41=0,"无效半径",IF(D41&lt;F41,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E41-C41)*1000/H41))))))</f>
-        <v>-29.235804568699994</v>
-      </c>
-      <c r="H41" s="15">
-        <f>IF(COUNT(C41:F41)&lt;4,"",1000*SQRT((C41-E41)^2+(D41-F41)^2))</f>
-        <v>153.5610627730872</v>
-      </c>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" s="11">
-        <v>1.306</v>
-      </c>
-      <c r="D42" s="11">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="E42" s="11">
-        <v>1.4550000000000001</v>
-      </c>
-      <c r="F42" s="11">
-        <v>0.26200000000000001</v>
-      </c>
-      <c r="G42" s="12">
-        <f>IF(COUNT(C42:F42)&lt;4,"",IF(H42=0,"无效半径",IF(D42&lt;F42,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E42-C42)*1000/H42))))))</f>
-        <v>13.21908490701656</v>
-      </c>
-      <c r="H42" s="14">
-        <f>IF(COUNT(C42:F42)&lt;4,"",1000*SQRT((C42-E42)^2+(D42-F42)^2))</f>
-        <v>153.05554547287727</v>
-      </c>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A46" s="2"/>
-      <c r="B46" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H46" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:9" ht="39.950000000000003" customHeight="1">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A48" s="2"/>
-      <c r="B48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E48" s="14">
-        <v>46</v>
-      </c>
-      <c r="F48" s="14">
-        <v>163</v>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A49" s="2"/>
-      <c r="B49" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E49" s="15">
-        <v>54</v>
-      </c>
-      <c r="F49" s="15">
-        <v>154</v>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50" s="14">
-        <v>83</v>
-      </c>
-      <c r="F50" s="14">
-        <v>163</v>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A51" s="2"/>
-      <c r="B51" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" s="15">
-        <v>111</v>
-      </c>
-      <c r="F51" s="15">
-        <v>154</v>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="1:9" ht="24" customHeight="1"/>
-    <row r="56" spans="1:9" ht="24" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="E32:H32"/>
-  </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF31475E"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="14.25"/>
+  <x:cols>
+    <x:col min="1" max="1" width="2.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="8" width="16.25" customWidth="1"/>
+    <x:col min="9" max="9" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="14" width="10" customWidth="1"/>
+    <x:col min="15" max="15" width="10.5" customWidth="1"/>
+    <x:col min="7" max="7" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="2.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="54"/>
+      <x:c r="B1" s="54"/>
+      <x:c r="C1" s="54"/>
+      <x:c r="D1" s="54"/>
+      <x:c r="E1" s="54"/>
+      <x:c r="F1" s="54"/>
+      <x:c r="G1" s="54"/>
+      <x:c r="H1" s="54"/>
+      <x:c r="I1" s="54"/>
+      <x:c r="J1" s="54"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="54"/>
+      <x:c r="B2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="C2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="D2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="E2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="F2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="G2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="H2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="I2" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="J2" s="54"/>
+    </x:row>
+    <x:row r="3" ht="27" customHeight="1">
+      <x:c r="A3" s="54"/>
+      <x:c r="B3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="C3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="D3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="E3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="F3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="G3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="H3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="I3" s="55" t="str">
+        <x:v>Astral · ARB Outer Parameters</x:v>
+      </x:c>
+      <x:c r="J3" s="54"/>
+    </x:row>
+    <x:row r="4" ht="27" customHeight="1">
+      <x:c r="A4" s="54"/>
+      <x:c r="B4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="C4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="F4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="G4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="H4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="J4" s="54"/>
+    </x:row>
+    <x:row r="5" ht="27" customHeight="1">
+      <x:c r="A5" s="54"/>
+      <x:c r="B5" s="54"/>
+      <x:c r="C5" s="54"/>
+      <x:c r="D5" s="54"/>
+      <x:c r="E5" s="54"/>
+      <x:c r="F5" s="54"/>
+      <x:c r="G5" s="54"/>
+      <x:c r="H5" s="54"/>
+      <x:c r="I5" s="54"/>
+      <x:c r="J5" s="54"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="54"/>
+      <x:c r="B6" s="60" t="str">
+        <x:v>Axle</x:v>
+      </x:c>
+      <x:c r="C6" s="60" t="str">
+        <x:v>Bar</x:v>
+      </x:c>
+      <x:c r="D6" s="60" t="str">
+        <x:v>Diameter
+(mm)</x:v>
+      </x:c>
+      <x:c r="E6" s="60" t="str">
+        <x:v>Torsion
+(N·m/rad)</x:v>
+      </x:c>
+      <x:c r="F6" s="54"/>
+      <x:c r="G6" s="54"/>
+      <x:c r="H6" s="54"/>
+      <x:c r="I6" s="54"/>
+      <x:c r="J6" s="54"/>
+    </x:row>
+    <x:row r="7" ht="27" customHeight="1">
+      <x:c r="A7" s="54"/>
+      <x:c r="B7" s="62" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="C7" s="62" t="str">
+        <x:v>Soft</x:v>
+      </x:c>
+      <x:c r="D7" s="67" t="n">
+        <x:v>14.6</x:v>
+      </x:c>
+      <x:c r="E7" s="69">
+        <x:f>$E$8*(D7/$D$8)^4</x:f>
+        <x:v>941.4063685268464</x:v>
+      </x:c>
+      <x:c r="F7" s="54"/>
+      <x:c r="G7" s="54"/>
+      <x:c r="H7" s="54"/>
+      <x:c r="I7" s="54"/>
+      <x:c r="J7" s="54"/>
+    </x:row>
+    <x:row r="8" ht="27" customHeight="1">
+      <x:c r="A8" s="54"/>
+      <x:c r="B8" s="63" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="C8" s="63" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D8" s="67" t="n">
+        <x:v>17.6</x:v>
+      </x:c>
+      <x:c r="E8" s="68" t="n">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="F8" s="54"/>
+      <x:c r="G8" s="54"/>
+      <x:c r="H8" s="54"/>
+      <x:c r="I8" s="54"/>
+      <x:c r="J8" s="54"/>
+    </x:row>
+    <x:row r="9" ht="27" customHeight="1">
+      <x:c r="A9" s="54"/>
+      <x:c r="B9" s="62" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="C9" s="62" t="str">
+        <x:v>Hard</x:v>
+      </x:c>
+      <x:c r="D9" s="67" t="n">
+        <x:v>20.5</x:v>
+      </x:c>
+      <x:c r="E9" s="69">
+        <x:f>$E$8*(D9/$D$8)^4</x:f>
+        <x:v>3659.1579207191103</x:v>
+      </x:c>
+      <x:c r="F9" s="54"/>
+      <x:c r="G9" s="54"/>
+      <x:c r="H9" s="54"/>
+      <x:c r="I9" s="54"/>
+      <x:c r="J9" s="54"/>
+    </x:row>
+    <x:row r="10" ht="27" customHeight="1">
+      <x:c r="A10" s="54"/>
+      <x:c r="B10" s="63" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="C10" s="63" t="str">
+        <x:v>Soft</x:v>
+      </x:c>
+      <x:c r="D10" s="67" t="n">
+        <x:v>16.2</x:v>
+      </x:c>
+      <x:c r="E10" s="70">
+        <x:f>$E$11*(D10/$D$11)^4</x:f>
+        <x:v>1429.067440624532</x:v>
+      </x:c>
+      <x:c r="F10" s="54"/>
+      <x:c r="G10" s="54"/>
+      <x:c r="H10" s="54"/>
+      <x:c r="I10" s="54"/>
+      <x:c r="J10" s="54"/>
+    </x:row>
+    <x:row r="11" ht="27" customHeight="1">
+      <x:c r="A11" s="54"/>
+      <x:c r="B11" s="62" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="C11" s="62" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D11" s="67" t="n">
+        <x:v>19.4</x:v>
+      </x:c>
+      <x:c r="E11" s="68" t="n">
+        <x:v>2939</x:v>
+      </x:c>
+      <x:c r="F11" s="54"/>
+      <x:c r="G11" s="54"/>
+      <x:c r="H11" s="54"/>
+      <x:c r="I11" s="54"/>
+      <x:c r="J11" s="54"/>
+    </x:row>
+    <x:row r="12" ht="27" customHeight="1">
+      <x:c r="A12" s="54"/>
+      <x:c r="B12" s="63" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="C12" s="63" t="str">
+        <x:v>Hard</x:v>
+      </x:c>
+      <x:c r="D12" s="67" t="n">
+        <x:v>22.1</x:v>
+      </x:c>
+      <x:c r="E12" s="70">
+        <x:f>$E$11*(D12/$D$11)^4</x:f>
+        <x:v>4949.504929094451</x:v>
+      </x:c>
+      <x:c r="F12" s="54"/>
+      <x:c r="G12" s="54"/>
+      <x:c r="H12" s="54"/>
+      <x:c r="I12" s="54"/>
+      <x:c r="J12" s="54"/>
+    </x:row>
+    <x:row r="13" ht="27" customHeight="1">
+      <x:c r="A13" s="54"/>
+      <x:c r="B13" s="54"/>
+      <x:c r="C13" s="54"/>
+      <x:c r="D13" s="54"/>
+      <x:c r="E13" s="54"/>
+      <x:c r="F13" s="54"/>
+      <x:c r="G13" s="54"/>
+      <x:c r="H13" s="54"/>
+      <x:c r="I13" s="54"/>
+      <x:c r="J13" s="54"/>
+    </x:row>
+    <x:row r="14" ht="27" customHeight="1">
+      <x:c r="A14" s="54"/>
+      <x:c r="B14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="C14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="D14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="E14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="F14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="G14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="H14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="I14" s="72" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="J14" s="54"/>
+    </x:row>
+    <x:row r="15" ht="27" customHeight="1">
+      <x:c r="A15" s="54"/>
+      <x:c r="B15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="C15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="D15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="E15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="F15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="G15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="H15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="I15" s="73" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="J15" s="54"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="54"/>
+      <x:c r="B16" s="60" t="str">
+        <x:v>Axle</x:v>
+      </x:c>
+      <x:c r="C16" s="60" t="str">
+        <x:v>arb1 Start Y
+(m)</x:v>
+      </x:c>
+      <x:c r="D16" s="60" t="str">
+        <x:v>arb1 Start Z
+(m)</x:v>
+      </x:c>
+      <x:c r="E16" s="60" t="str">
+        <x:v>arb2 Y
+(m)</x:v>
+      </x:c>
+      <x:c r="F16" s="60" t="str">
+        <x:v>arb2 Z
+(m)</x:v>
+      </x:c>
+      <x:c r="G16" s="60" t="str">
+        <x:v>Start angle
+(°)</x:v>
+      </x:c>
+      <x:c r="H16" s="60" t="str">
+        <x:v>Radius
+(mm)</x:v>
+      </x:c>
+      <x:c r="I16" s="54"/>
+      <x:c r="J16" s="54"/>
+    </x:row>
+    <x:row r="17" ht="27" customHeight="1">
+      <x:c r="A17" s="54"/>
+      <x:c r="B17" s="62" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="C17" s="74" t="n">
+        <x:v>-1.061</x:v>
+      </x:c>
+      <x:c r="D17" s="74" t="n">
+        <x:v>0.195</x:v>
+      </x:c>
+      <x:c r="E17" s="74" t="n">
+        <x:v>-0.899</x:v>
+      </x:c>
+      <x:c r="F17" s="74" t="n">
+        <x:v>0.185</x:v>
+      </x:c>
+      <x:c r="G17" s="75">
+        <x:f>IF(COUNT(C17:F17)&lt;4,"",IF(H17=0,"无效半径",IF(D17&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-C17)*1000/H17))))))</x:f>
+        <x:v>3.532294583890938</x:v>
+      </x:c>
+      <x:c r="H17" s="77">
+        <x:f>IF(COUNT(C17:F17)&lt;4,"",1000*SQRT((C17-E17)^2+(D17-F17)^2))</x:f>
+        <x:v>162.30834852218777</x:v>
+      </x:c>
+      <x:c r="I17" s="54"/>
+      <x:c r="J17" s="54"/>
+    </x:row>
+    <x:row r="18" ht="27" customHeight="1">
+      <x:c r="A18" s="54"/>
+      <x:c r="B18" s="63" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="C18" s="74" t="n">
+        <x:v>1.321</x:v>
+      </x:c>
+      <x:c r="D18" s="74" t="n">
+        <x:v>0.186</x:v>
+      </x:c>
+      <x:c r="E18" s="74" t="n">
+        <x:v>1.455</x:v>
+      </x:c>
+      <x:c r="F18" s="74" t="n">
+        <x:v>0.261</x:v>
+      </x:c>
+      <x:c r="G18" s="76">
+        <x:f>IF(COUNT(C18:F18)&lt;4,"",IF(H18=0,"无效半径",IF(D18&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-C18)*1000/H18))))))</x:f>
+        <x:v>-29.235804568699994</x:v>
+      </x:c>
+      <x:c r="H18" s="78">
+        <x:f>IF(COUNT(C18:F18)&lt;4,"",1000*SQRT((C18-E18)^2+(D18-F18)^2))</x:f>
+        <x:v>153.5610627730872</x:v>
+      </x:c>
+      <x:c r="I18" s="54"/>
+      <x:c r="J18" s="54"/>
+    </x:row>
+    <x:row r="19" ht="27" customHeight="1">
+      <x:c r="A19" s="54"/>
+      <x:c r="B19" s="54"/>
+      <x:c r="C19" s="54"/>
+      <x:c r="D19" s="54"/>
+      <x:c r="E19" s="54"/>
+      <x:c r="F19" s="54"/>
+      <x:c r="G19" s="54"/>
+      <x:c r="H19" s="54"/>
+      <x:c r="I19" s="54"/>
+      <x:c r="J19" s="54"/>
+    </x:row>
+    <x:row r="20" ht="27" customHeight="1">
+      <x:c r="A20" s="54"/>
+      <x:c r="B20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="C20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="D20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="E20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="F20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="G20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="H20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="I20" s="72" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="J20" s="54"/>
+    </x:row>
+    <x:row r="21" ht="27" customHeight="1">
+      <x:c r="A21" s="54"/>
+      <x:c r="B21" s="54"/>
+      <x:c r="C21" s="54"/>
+      <x:c r="D21" s="54"/>
+      <x:c r="E21" s="54"/>
+      <x:c r="F21" s="54"/>
+      <x:c r="G21" s="54"/>
+      <x:c r="H21" s="54"/>
+      <x:c r="I21" s="54"/>
+      <x:c r="J21" s="54"/>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="54"/>
+      <x:c r="B22" s="60" t="str">
+        <x:v>Surface</x:v>
+      </x:c>
+      <x:c r="C22" s="60" t="str">
+        <x:v>Axle</x:v>
+      </x:c>
+      <x:c r="D22" s="60" t="str">
+        <x:v>Position</x:v>
+      </x:c>
+      <x:c r="E22" s="60" t="str">
+        <x:v>Wheel ΔZ
+(mm)</x:v>
+      </x:c>
+      <x:c r="F22" s="60" t="str">
+        <x:v>arb1 End Y
+(m)</x:v>
+      </x:c>
+      <x:c r="G22" s="60" t="str">
+        <x:v>arb1 End Z
+(m)</x:v>
+      </x:c>
+      <x:c r="H22" s="60" t="str">
+        <x:v>End angle
+(°)</x:v>
+      </x:c>
+      <x:c r="I22" s="60" t="str">
+        <x:v>Radius
+(mm)</x:v>
+      </x:c>
+      <x:c r="J22" s="54"/>
+    </x:row>
+    <x:row r="23" ht="27" customHeight="1">
+      <x:c r="A23" s="54"/>
+      <x:c r="B23" s="62" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C23" s="62" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D23" s="62" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E23" s="67" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F23" s="74" t="n">
+        <x:v>-1.046</x:v>
+      </x:c>
+      <x:c r="G23" s="74" t="n">
+        <x:v>0.254</x:v>
+      </x:c>
+      <x:c r="H23" s="75">
+        <x:f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",IF(I23=0,"无效半径",IF(G23&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F23)*1000/I23))))))</x:f>
+        <x:v>25.144785630678925</x:v>
+      </x:c>
+      <x:c r="I23" s="77">
+        <x:f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",1000*SQRT((F23-E17)^2+(G23-F17)^2))</x:f>
+        <x:v>162.3884232326923</x:v>
+      </x:c>
+      <x:c r="J23" s="54"/>
+    </x:row>
+    <x:row r="24" ht="27" customHeight="1">
+      <x:c r="A24" s="54"/>
+      <x:c r="B24" s="63" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E24" s="67" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F24" s="74" t="n">
+        <x:v>1.301</x:v>
+      </x:c>
+      <x:c r="G24" s="74" t="n">
+        <x:v>0.259</x:v>
+      </x:c>
+      <x:c r="H24" s="76">
+        <x:f>IF(COUNT(F24:G24,E18:F18)&lt;4,"",IF(I24=0,"无效半径",IF(G24&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F24)*1000/I24))))))</x:f>
+        <x:v>-0.7440592028885111</x:v>
+      </x:c>
+      <x:c r="I24" s="78">
+        <x:f>IF(COUNT(F24:G24,E18:F18)&lt;4,"",1000*SQRT((F24-E18)^2+(G24-F18)^2))</x:f>
+        <x:v>154.0129864654278</x:v>
+      </x:c>
+      <x:c r="J24" s="54"/>
+    </x:row>
+    <x:row r="25" ht="27" customHeight="1">
+      <x:c r="A25" s="54"/>
+      <x:c r="B25" s="62" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C25" s="62" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D25" s="62" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E25" s="67" t="n">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F25" s="74" t="n">
+        <x:v>-1.032</x:v>
+      </x:c>
+      <x:c r="G25" s="74" t="n">
+        <x:v>0.278</x:v>
+      </x:c>
+      <x:c r="H25" s="75">
+        <x:f>IF(COUNT(F25:G25,E17:F17)&lt;4,"",IF(I25=0,"无效半径",IF(G25&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F25)*1000/I25))))))</x:f>
+        <x:v>34.963097546036515</x:v>
+      </x:c>
+      <x:c r="I25" s="77">
+        <x:f>IF(COUNT(F25:G25,E17:F17)&lt;4,"",1000*SQRT((F25-E17)^2+(G25-F17)^2))</x:f>
+        <x:v>162.28986413205234</x:v>
+      </x:c>
+      <x:c r="J25" s="54"/>
+    </x:row>
+    <x:row r="26" ht="27" customHeight="1">
+      <x:c r="A26" s="54"/>
+      <x:c r="B26" s="63" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C26" s="63" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D26" s="63" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E26" s="67" t="n">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F26" s="74" t="n">
+        <x:v>1.306</x:v>
+      </x:c>
+      <x:c r="G26" s="74" t="n">
+        <x:v>0.297</x:v>
+      </x:c>
+      <x:c r="H26" s="76">
+        <x:f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",IF(I26=0,"无效半径",IF(G26&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F26)*1000/I26))))))</x:f>
+        <x:v>13.582963529836704</x:v>
+      </x:c>
+      <x:c r="I26" s="78">
+        <x:f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",1000*SQRT((F26-E18)^2+(G26-F18)^2))</x:f>
+        <x:v>153.28731193415848</x:v>
+      </x:c>
+      <x:c r="J26" s="54"/>
+    </x:row>
+    <x:row r="27" ht="27" customHeight="1">
+      <x:c r="A27" s="54"/>
+      <x:c r="B27" s="54"/>
+      <x:c r="C27" s="54"/>
+      <x:c r="D27" s="54"/>
+      <x:c r="E27" s="54"/>
+      <x:c r="F27" s="54"/>
+      <x:c r="G27" s="54"/>
+      <x:c r="H27" s="54"/>
+      <x:c r="I27" s="54"/>
+      <x:c r="J27" s="54"/>
+    </x:row>
+    <x:row r="28" ht="27" customHeight="1">
+      <x:c r="A28" s="54"/>
+      <x:c r="B28" s="54"/>
+      <x:c r="C28" s="54"/>
+      <x:c r="D28" s="54"/>
+      <x:c r="E28" s="54"/>
+      <x:c r="F28" s="54"/>
+      <x:c r="G28" s="54"/>
+      <x:c r="H28" s="54"/>
+      <x:c r="I28" s="54"/>
+      <x:c r="J28" s="54"/>
+    </x:row>
+    <x:row r="29" ht="27" customHeight="1">
+      <x:c r="A29" s="54"/>
+      <x:c r="B29" s="54"/>
+      <x:c r="C29" s="54"/>
+      <x:c r="D29" s="54"/>
+      <x:c r="E29" s="54"/>
+      <x:c r="F29" s="54"/>
+      <x:c r="G29" s="54"/>
+      <x:c r="H29" s="54"/>
+      <x:c r="I29" s="54"/>
+      <x:c r="J29" s="54"/>
+    </x:row>
+    <x:row r="30" ht="27" customHeight="1">
+      <x:c r="A30" s="54"/>
+      <x:c r="B30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="C30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="D30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="E30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="F30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="G30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="H30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="I30" s="72" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="J30" s="54"/>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="54"/>
+      <x:c r="B31" s="60" t="str">
+        <x:v>Surface</x:v>
+      </x:c>
+      <x:c r="C31" s="60" t="str">
+        <x:v>Axle</x:v>
+      </x:c>
+      <x:c r="D31" s="60" t="str">
+        <x:v>Position</x:v>
+      </x:c>
+      <x:c r="E31" s="60" t="str">
+        <x:v>ARB ΔZ (mm)</x:v>
+      </x:c>
+      <x:c r="F31" s="60" t="str">
+        <x:v>Original arm (mm)</x:v>
+      </x:c>
+      <x:c r="G31" s="54"/>
+      <x:c r="H31" s="54"/>
+      <x:c r="I31" s="54"/>
+      <x:c r="J31" s="54"/>
+    </x:row>
+    <x:row r="32" ht="27" customHeight="1">
+      <x:c r="A32" s="54"/>
+      <x:c r="B32" s="63" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C32" s="63" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D32" s="63" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E32" s="78" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F32" s="78" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G32" s="54"/>
+      <x:c r="H32" s="54"/>
+      <x:c r="I32" s="54"/>
+      <x:c r="J32" s="54"/>
+    </x:row>
+    <x:row r="33" ht="27" customHeight="1">
+      <x:c r="A33" s="54"/>
+      <x:c r="B33" s="62" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C33" s="62" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D33" s="62" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E33" s="77" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F33" s="77" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G33" s="54"/>
+      <x:c r="H33" s="54"/>
+      <x:c r="I33" s="54"/>
+      <x:c r="J33" s="54"/>
+    </x:row>
+    <x:row r="34" ht="27" customHeight="1">
+      <x:c r="A34" s="54"/>
+      <x:c r="B34" s="63" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C34" s="63" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D34" s="63" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E34" s="78" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F34" s="78" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G34" s="54"/>
+      <x:c r="H34" s="54"/>
+      <x:c r="I34" s="54"/>
+      <x:c r="J34" s="54"/>
+    </x:row>
+    <x:row r="35" ht="27" customHeight="1">
+      <x:c r="A35" s="54"/>
+      <x:c r="B35" s="62" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C35" s="62" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D35" s="62" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E35" s="77" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F35" s="77" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G35" s="54"/>
+      <x:c r="H35" s="54"/>
+      <x:c r="I35" s="54"/>
+      <x:c r="J35" s="54"/>
+    </x:row>
+    <x:row r="36" ht="27" customHeight="1">
+      <x:c r="A36" s="54"/>
+      <x:c r="B36" s="54"/>
+      <x:c r="C36" s="54"/>
+      <x:c r="D36" s="54"/>
+      <x:c r="E36" s="54"/>
+      <x:c r="F36" s="54"/>
+      <x:c r="G36" s="54"/>
+      <x:c r="H36" s="54"/>
+      <x:c r="I36" s="54"/>
+      <x:c r="J36" s="54"/>
+    </x:row>
+    <x:row r="37" ht="27" customHeight="1">
+      <x:c r="A37" s="54"/>
+      <x:c r="B37" s="54"/>
+      <x:c r="C37" s="54"/>
+      <x:c r="D37" s="54"/>
+      <x:c r="E37" s="54"/>
+      <x:c r="F37" s="54"/>
+      <x:c r="G37" s="54"/>
+      <x:c r="H37" s="54"/>
+      <x:c r="I37" s="54"/>
+      <x:c r="J37" s="54"/>
+    </x:row>
+    <x:row r="38" ht="27" customHeight="1">
+      <x:c r="A38" s="54"/>
+      <x:c r="B38" s="54"/>
+      <x:c r="C38" s="54"/>
+      <x:c r="D38" s="54"/>
+      <x:c r="E38" s="54"/>
+      <x:c r="F38" s="54"/>
+      <x:c r="G38" s="54"/>
+      <x:c r="H38" s="54"/>
+      <x:c r="I38" s="54"/>
+      <x:c r="J38" s="54"/>
+    </x:row>
+    <x:row r="39" ht="27" customHeight="1">
+      <x:c r="A39" s="54"/>
+      <x:c r="B39" s="54"/>
+      <x:c r="C39" s="54"/>
+      <x:c r="D39" s="54"/>
+      <x:c r="E39" s="54"/>
+      <x:c r="F39" s="54"/>
+      <x:c r="G39" s="54"/>
+      <x:c r="H39" s="54"/>
+      <x:c r="I39" s="54"/>
+      <x:c r="J39" s="54"/>
+    </x:row>
+    <x:row r="40" ht="27" customHeight="1">
+      <x:c r="A40" s="54"/>
+      <x:c r="B40" s="54"/>
+      <x:c r="C40" s="54"/>
+      <x:c r="D40" s="54"/>
+      <x:c r="E40" s="54"/>
+      <x:c r="F40" s="54"/>
+      <x:c r="G40" s="54"/>
+      <x:c r="H40" s="54"/>
+      <x:c r="I40" s="54"/>
+      <x:c r="J40" s="54"/>
+    </x:row>
+    <x:row r="41" ht="27" customHeight="1">
+      <x:c r="A41" s="54"/>
+      <x:c r="B41" s="54"/>
+      <x:c r="C41" s="54"/>
+      <x:c r="D41" s="54"/>
+      <x:c r="E41" s="54"/>
+      <x:c r="F41" s="54"/>
+      <x:c r="G41" s="54"/>
+      <x:c r="H41" s="54"/>
+      <x:c r="I41" s="54"/>
+      <x:c r="J41" s="54"/>
+    </x:row>
+    <x:row r="42" ht="27" customHeight="1">
+      <x:c r="A42" s="54"/>
+      <x:c r="B42" s="54"/>
+      <x:c r="C42" s="54"/>
+      <x:c r="D42" s="54"/>
+      <x:c r="E42" s="54"/>
+      <x:c r="F42" s="54"/>
+      <x:c r="G42" s="54"/>
+      <x:c r="H42" s="54"/>
+      <x:c r="I42" s="54"/>
+      <x:c r="J42" s="54"/>
+    </x:row>
+    <x:row r="43" ht="27" customHeight="1">
+      <x:c r="A43" s="54"/>
+      <x:c r="B43" s="54"/>
+      <x:c r="C43" s="54"/>
+      <x:c r="D43" s="54"/>
+      <x:c r="E43" s="54"/>
+      <x:c r="F43" s="54"/>
+      <x:c r="G43" s="54"/>
+      <x:c r="H43" s="54"/>
+      <x:c r="I43" s="54"/>
+      <x:c r="J43" s="54"/>
+    </x:row>
+    <x:row r="44" ht="27" customHeight="1">
+      <x:c r="A44" s="54"/>
+      <x:c r="B44" s="54"/>
+      <x:c r="C44" s="54"/>
+      <x:c r="D44" s="54"/>
+      <x:c r="E44" s="54"/>
+      <x:c r="F44" s="54"/>
+      <x:c r="G44" s="54"/>
+      <x:c r="H44" s="54"/>
+      <x:c r="I44" s="54"/>
+      <x:c r="J44" s="54"/>
+    </x:row>
+    <x:row r="45" ht="27" customHeight="1">
+      <x:c r="A45" s="54"/>
+      <x:c r="B45" s="54"/>
+      <x:c r="C45" s="54"/>
+      <x:c r="D45" s="54"/>
+      <x:c r="E45" s="54"/>
+      <x:c r="F45" s="54"/>
+      <x:c r="G45" s="54"/>
+      <x:c r="H45" s="54"/>
+      <x:c r="I45" s="54"/>
+      <x:c r="J45" s="54"/>
+    </x:row>
+    <x:row r="46" ht="27" customHeight="1">
+      <x:c r="A46" s="54"/>
+      <x:c r="B46" s="54"/>
+      <x:c r="C46" s="54"/>
+      <x:c r="D46" s="54"/>
+      <x:c r="E46" s="54"/>
+      <x:c r="F46" s="54"/>
+      <x:c r="G46" s="54"/>
+      <x:c r="H46" s="54"/>
+      <x:c r="I46" s="54"/>
+      <x:c r="J46" s="54"/>
+    </x:row>
+    <x:row r="47" ht="27" customHeight="1">
+      <x:c r="A47" s="54"/>
+      <x:c r="B47" s="54"/>
+      <x:c r="C47" s="54"/>
+      <x:c r="D47" s="54"/>
+      <x:c r="E47" s="54"/>
+      <x:c r="F47" s="54"/>
+      <x:c r="G47" s="54"/>
+      <x:c r="H47" s="54"/>
+      <x:c r="I47" s="54"/>
+      <x:c r="J47" s="54"/>
+    </x:row>
+    <x:row r="48" ht="27" customHeight="1">
+      <x:c r="A48" s="54"/>
+      <x:c r="B48" s="54"/>
+      <x:c r="C48" s="54"/>
+      <x:c r="D48" s="54"/>
+      <x:c r="E48" s="54"/>
+      <x:c r="F48" s="54"/>
+      <x:c r="G48" s="54"/>
+      <x:c r="H48" s="54"/>
+      <x:c r="I48" s="54"/>
+      <x:c r="J48" s="54"/>
+    </x:row>
+    <x:row r="49" ht="27" customHeight="1">
+      <x:c r="A49" s="54"/>
+      <x:c r="B49" s="54"/>
+      <x:c r="C49" s="54"/>
+      <x:c r="D49" s="54"/>
+      <x:c r="E49" s="54"/>
+      <x:c r="F49" s="54"/>
+      <x:c r="G49" s="54"/>
+      <x:c r="H49" s="54"/>
+      <x:c r="I49" s="54"/>
+      <x:c r="J49" s="54"/>
+    </x:row>
+    <x:row r="50" ht="27" customHeight="1">
+      <x:c r="A50" s="54"/>
+      <x:c r="B50" s="54"/>
+      <x:c r="C50" s="54"/>
+      <x:c r="D50" s="54"/>
+      <x:c r="E50" s="54"/>
+      <x:c r="F50" s="54"/>
+      <x:c r="G50" s="54"/>
+      <x:c r="H50" s="54"/>
+      <x:c r="I50" s="54"/>
+      <x:c r="J50" s="54"/>
+    </x:row>
+    <x:row r="51" ht="27" customHeight="1">
+      <x:c r="A51" s="54"/>
+      <x:c r="B51" s="54"/>
+      <x:c r="C51" s="54"/>
+      <x:c r="D51" s="54"/>
+      <x:c r="E51" s="54"/>
+      <x:c r="F51" s="54"/>
+      <x:c r="G51" s="54"/>
+      <x:c r="H51" s="54"/>
+      <x:c r="I51" s="54"/>
+      <x:c r="J51" s="54"/>
+    </x:row>
+    <x:row r="52" ht="27" customHeight="1">
+      <x:c r="A52" s="54"/>
+      <x:c r="B52" s="54"/>
+      <x:c r="C52" s="54"/>
+      <x:c r="D52" s="54"/>
+      <x:c r="E52" s="54"/>
+      <x:c r="F52" s="54"/>
+      <x:c r="G52" s="54"/>
+      <x:c r="H52" s="54"/>
+      <x:c r="I52" s="54"/>
+      <x:c r="J52" s="54"/>
+    </x:row>
+    <x:row r="53" ht="27" customHeight="1">
+      <x:c r="A53" s="54"/>
+      <x:c r="B53" s="54"/>
+      <x:c r="C53" s="54"/>
+      <x:c r="D53" s="54"/>
+      <x:c r="E53" s="54"/>
+      <x:c r="F53" s="54"/>
+      <x:c r="G53" s="54"/>
+      <x:c r="H53" s="54"/>
+      <x:c r="I53" s="54"/>
+      <x:c r="J53" s="54"/>
+    </x:row>
+    <x:row r="54" ht="27" customHeight="1">
+      <x:c r="A54" s="54"/>
+      <x:c r="B54" s="54"/>
+      <x:c r="C54" s="54"/>
+      <x:c r="D54" s="54"/>
+      <x:c r="E54" s="54"/>
+      <x:c r="F54" s="54"/>
+      <x:c r="G54" s="54"/>
+      <x:c r="H54" s="54"/>
+      <x:c r="I54" s="54"/>
+      <x:c r="J54" s="54"/>
+    </x:row>
+    <x:row r="55" ht="27" customHeight="1">
+      <x:c r="A55" s="54"/>
+      <x:c r="B55" s="54"/>
+      <x:c r="C55" s="54"/>
+      <x:c r="D55" s="54"/>
+      <x:c r="E55" s="54"/>
+      <x:c r="F55" s="54"/>
+      <x:c r="G55" s="54"/>
+      <x:c r="H55" s="54"/>
+      <x:c r="I55" s="54"/>
+      <x:c r="J55" s="54"/>
+    </x:row>
+    <x:row r="56" ht="27" customHeight="1">
+      <x:c r="A56" s="54"/>
+      <x:c r="B56" s="54"/>
+      <x:c r="C56" s="54"/>
+      <x:c r="D56" s="54"/>
+      <x:c r="E56" s="54"/>
+      <x:c r="F56" s="54"/>
+      <x:c r="G56" s="54"/>
+      <x:c r="H56" s="54"/>
+      <x:c r="I56" s="54"/>
+      <x:c r="J56" s="54"/>
+    </x:row>
+    <x:row r="57" ht="27" customHeight="1">
+      <x:c r="A57" s="54"/>
+      <x:c r="B57" s="54"/>
+      <x:c r="C57" s="54"/>
+      <x:c r="D57" s="54"/>
+      <x:c r="E57" s="54"/>
+      <x:c r="F57" s="54"/>
+      <x:c r="G57" s="54"/>
+      <x:c r="H57" s="54"/>
+      <x:c r="I57" s="54"/>
+      <x:c r="J57" s="54"/>
+    </x:row>
+    <x:row r="58" ht="27" customHeight="1">
+      <x:c r="A58" s="54"/>
+      <x:c r="B58" s="54"/>
+      <x:c r="C58" s="54"/>
+      <x:c r="D58" s="54"/>
+      <x:c r="E58" s="54"/>
+      <x:c r="F58" s="54"/>
+      <x:c r="G58" s="54"/>
+      <x:c r="H58" s="54"/>
+      <x:c r="I58" s="54"/>
+      <x:c r="J58" s="54"/>
+    </x:row>
+    <x:row r="59" ht="27" customHeight="1">
+      <x:c r="A59" s="54"/>
+      <x:c r="B59" s="54"/>
+      <x:c r="C59" s="54"/>
+      <x:c r="D59" s="54"/>
+      <x:c r="E59" s="54"/>
+      <x:c r="F59" s="54"/>
+      <x:c r="G59" s="54"/>
+      <x:c r="H59" s="54"/>
+      <x:c r="I59" s="54"/>
+      <x:c r="J59" s="54"/>
+    </x:row>
+    <x:row r="60" ht="27" customHeight="1">
+      <x:c r="A60" s="54"/>
+      <x:c r="B60" s="54"/>
+      <x:c r="C60" s="54"/>
+      <x:c r="D60" s="54"/>
+      <x:c r="E60" s="54"/>
+      <x:c r="F60" s="54"/>
+      <x:c r="G60" s="54"/>
+      <x:c r="H60" s="54"/>
+      <x:c r="I60" s="54"/>
+      <x:c r="J60" s="54"/>
+    </x:row>
+    <x:row r="61" ht="27" customHeight="1">
+      <x:c r="A61" s="54"/>
+      <x:c r="B61" s="54"/>
+      <x:c r="C61" s="54"/>
+      <x:c r="D61" s="54"/>
+      <x:c r="E61" s="54"/>
+      <x:c r="F61" s="54"/>
+      <x:c r="G61" s="54"/>
+      <x:c r="H61" s="54"/>
+      <x:c r="I61" s="54"/>
+      <x:c r="J61" s="54"/>
+    </x:row>
+    <x:row r="62" ht="27" customHeight="1">
+      <x:c r="A62" s="54"/>
+      <x:c r="B62" s="54"/>
+      <x:c r="C62" s="54"/>
+      <x:c r="D62" s="54"/>
+      <x:c r="E62" s="54"/>
+      <x:c r="F62" s="54"/>
+      <x:c r="G62" s="54"/>
+      <x:c r="H62" s="54"/>
+      <x:c r="I62" s="54"/>
+      <x:c r="J62" s="54"/>
+    </x:row>
+    <x:row r="63" ht="27" customHeight="1">
+      <x:c r="A63" s="54"/>
+      <x:c r="B63" s="54"/>
+      <x:c r="C63" s="54"/>
+      <x:c r="D63" s="54"/>
+      <x:c r="E63" s="54"/>
+      <x:c r="F63" s="54"/>
+      <x:c r="G63" s="54"/>
+      <x:c r="H63" s="54"/>
+      <x:c r="I63" s="54"/>
+      <x:c r="J63" s="54"/>
+    </x:row>
+    <x:row r="64" ht="27" customHeight="1">
+      <x:c r="A64" s="54"/>
+      <x:c r="B64" s="54"/>
+      <x:c r="C64" s="54"/>
+      <x:c r="D64" s="54"/>
+      <x:c r="E64" s="54"/>
+      <x:c r="F64" s="54"/>
+      <x:c r="G64" s="54"/>
+      <x:c r="H64" s="54"/>
+      <x:c r="I64" s="54"/>
+      <x:c r="J64" s="54"/>
+    </x:row>
+    <x:row r="65" ht="27" customHeight="1">
+      <x:c r="A65" s="54"/>
+      <x:c r="B65" s="54"/>
+      <x:c r="C65" s="54"/>
+      <x:c r="D65" s="54"/>
+      <x:c r="E65" s="54"/>
+      <x:c r="F65" s="54"/>
+      <x:c r="G65" s="54"/>
+      <x:c r="H65" s="54"/>
+      <x:c r="I65" s="54"/>
+      <x:c r="J65" s="54"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="B2:I3"/>
+    <x:mergeCell ref="B4:I4"/>
+    <x:mergeCell ref="B14:I14"/>
+    <x:mergeCell ref="B15:I15"/>
+    <x:mergeCell ref="B20:I20"/>
+    <x:mergeCell ref="B30:I30"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3531,20 +3933,20 @@
         <v>38</v>
       </c>
       <c r="E6" s="14">
-        <f>IF(ISNUMBER(Parameters!C18),Parameters!C18,"")</f>
+        <f>IF(ISNUMBER(Parameters!E23),Parameters!E23,"")</f>
         <v>167</v>
       </c>
       <c r="F6" s="16">
-        <f>IF(COUNT(Parameters!G20:G21)&lt;2,"",MOD(Parameters!G21-Parameters!G20+180,360)-180)</f>
+        <f>IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"",MOD(Parameters!H23-Parameters!G17+180,360)-180)</f>
         <v>21.612491046787994</v>
       </c>
       <c r="G6" s="18">
         <f>IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
-        <v>2.2587372953547687E-3</v>
+        <v>0.0022587372953547687</v>
       </c>
       <c r="H6" s="12">
         <f>IF(ISNUMBER(G6),1000*Parameters!E7*G6^2,"")</f>
-        <v>4.8029556626481638</v>
+        <v>4.802955662648164</v>
       </c>
       <c r="I6" s="12">
         <f>IF(ISNUMBER(G6),1000*Parameters!E8*G6^2,"")</f>
@@ -3552,10 +3954,10 @@
       </c>
       <c r="J6" s="12">
         <f>IF(ISNUMBER(G6),1000*Parameters!E9*G6^2,"")</f>
-        <v>18.6686364607279</v>
+        <v>18.668636460727903</v>
       </c>
       <c r="K6" s="20" t="str">
-        <f>IF(COUNT(Parameters!C20:F21)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G20:G21)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:F17,Parameters!F23:G23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"无效半径",""))))</f>
         <v/>
       </c>
       <c r="L6" s="2"/>
@@ -3573,20 +3975,20 @@
         <v>38</v>
       </c>
       <c r="E7" s="15">
-        <f>IF(ISNUMBER(Parameters!C25),Parameters!C25,"")</f>
+        <f>IF(ISNUMBER(Parameters!E24),Parameters!E24,"")</f>
         <v>166</v>
       </c>
       <c r="F7" s="17">
-        <f>IF(COUNT(Parameters!G27:G28)&lt;2,"",MOD(Parameters!G28-Parameters!G27+180,360)-180)</f>
+        <f>IF(COUNT(Parameters!G18,Parameters!H24)&lt;2,"",MOD(Parameters!H24-Parameters!G18+180,360)-180)</f>
         <v>28.491745365811482</v>
       </c>
       <c r="G7" s="19">
         <f>IF(COUNT(E7:F7)&lt;2,"",IF(E7&lt;=0,"",RADIANS(F7)/E7))</f>
-        <v>2.9956311221279912E-3</v>
+        <v>0.002995631122127991</v>
       </c>
       <c r="H7" s="13">
         <f>IF(ISNUMBER(G7),1000*Parameters!E10*G7^2,"")</f>
-        <v>12.824173715651447</v>
+        <v>12.824173715651444</v>
       </c>
       <c r="I7" s="13">
         <f>IF(ISNUMBER(G7),1000*Parameters!E11*G7^2,"")</f>
@@ -3597,7 +3999,7 @@
         <v>44.415896138142486</v>
       </c>
       <c r="K7" s="21" t="str">
-        <f>IF(COUNT(Parameters!C27:F28)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G27:G28)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:F18,Parameters!F24:G24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H24)&lt;2,"无效半径",""))))</f>
         <v/>
       </c>
       <c r="L7" s="2"/>
@@ -3615,31 +4017,31 @@
         <v>38</v>
       </c>
       <c r="E8" s="14">
-        <f>IF(ISNUMBER(Parameters!C32),Parameters!C32,"")</f>
+        <f>IF(ISNUMBER(Parameters!E25),Parameters!E25,"")</f>
         <v>266</v>
       </c>
       <c r="F8" s="16">
-        <f>IF(COUNT(Parameters!G34:G35)&lt;2,"",MOD(Parameters!G35-Parameters!G34+180,360)-180)</f>
+        <f>IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"",MOD(Parameters!H25-Parameters!G17+180,360)-180)</f>
         <v>31.430802962145577</v>
       </c>
       <c r="G8" s="18">
         <f>IF(COUNT(E8:F8)&lt;2,"",IF(E8&lt;=0,"",RADIANS(F8)/E8))</f>
-        <v>2.062296985845966E-3</v>
+        <v>0.002062296985845966</v>
       </c>
       <c r="H8" s="12">
         <f>IF(ISNUMBER(G8),1000*Parameters!E7*G8^2,"")</f>
-        <v>4.0038661085437566</v>
+        <v>4.003866108543757</v>
       </c>
       <c r="I8" s="12">
         <f>IF(ISNUMBER(G8),1000*Parameters!E8*G8^2,"")</f>
-        <v>8.4551008893647595</v>
+        <v>8.45510088936476</v>
       </c>
       <c r="J8" s="12">
         <f>IF(ISNUMBER(G8),1000*Parameters!E9*G8^2,"")</f>
-        <v>15.562650598490066</v>
+        <v>15.56265059849007</v>
       </c>
       <c r="K8" s="20" t="str">
-        <f>IF(COUNT(Parameters!C34:F35)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G34:G35)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:F17,Parameters!F25:G25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"无效半径",""))))</f>
         <v/>
       </c>
       <c r="L8" s="2"/>
@@ -3657,31 +4059,31 @@
         <v>38</v>
       </c>
       <c r="E9" s="15">
-        <f>IF(ISNUMBER(Parameters!C39),Parameters!C39,"")</f>
+        <f>IF(ISNUMBER(Parameters!E26),Parameters!E26,"")</f>
         <v>268</v>
       </c>
       <c r="F9" s="17">
-        <f>IF(COUNT(Parameters!G41:G42)&lt;2,"",MOD(Parameters!G42-Parameters!G41+180,360)-180)</f>
-        <v>42.454889475716556</v>
+        <f>IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"",MOD(Parameters!H26-Parameters!G18+180,360)-180)</f>
+        <v>42.81876809853668</v>
       </c>
       <c r="G9" s="19">
         <f>IF(COUNT(E9:F9)&lt;2,"",IF(E9&lt;=0,"",RADIANS(F9)/E9))</f>
-        <v>2.7648418094087428E-3</v>
+        <v>0.0027885391230126</v>
       </c>
       <c r="H9" s="13">
         <f>IF(ISNUMBER(G9),1000*Parameters!E10*G9^2,"")</f>
-        <v>10.924292019930764</v>
+        <v>11.112357594531261</v>
       </c>
       <c r="I9" s="13">
         <f>IF(ISNUMBER(G9),1000*Parameters!E11*G9^2,"")</f>
-        <v>22.4667453290695</v>
+        <v>22.853518344840758</v>
       </c>
       <c r="J9" s="13">
         <f>IF(ISNUMBER(G9),1000*Parameters!E12*G9^2,"")</f>
-        <v>37.835749148329093</v>
+        <v>38.48710503400469</v>
       </c>
       <c r="K9" s="21" t="str">
-        <f>IF(COUNT(Parameters!C41:F42)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G41:G42)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:F18,Parameters!F26:G26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"无效半径",""))))</f>
         <v/>
       </c>
       <c r="L9" s="2"/>
@@ -3775,11 +4177,11 @@
       </c>
       <c r="C15" s="13">
         <f>IF(ISNUMBER(H8),H8,NA())</f>
-        <v>4.0038661085437566</v>
+        <v>4.003866108543757</v>
       </c>
       <c r="D15" s="13">
         <f>IF(ISNUMBER(H9),H9,NA())</f>
-        <v>10.924292019930764</v>
+        <v>11.112357594531261</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -3798,11 +4200,11 @@
       </c>
       <c r="C16" s="12">
         <f>IF(ISNUMBER(I8),I8,NA())</f>
-        <v>8.4551008893647595</v>
+        <v>8.45510088936476</v>
       </c>
       <c r="D16" s="12">
         <f>IF(ISNUMBER(I9),I9,NA())</f>
-        <v>22.4667453290695</v>
+        <v>22.853518344840758</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -3821,11 +4223,11 @@
       </c>
       <c r="C17" s="13">
         <f>IF(ISNUMBER(J8),J8,NA())</f>
-        <v>15.562650598490066</v>
+        <v>15.56265059849007</v>
       </c>
       <c r="D17" s="13">
         <f>IF(ISNUMBER(J9),J9,NA())</f>
-        <v>37.835749148329093</v>
+        <v>38.48710503400469</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -3910,11 +4312,11 @@
       </c>
       <c r="C22" s="12">
         <f>IF(ISNUMBER(H6),H6,NA())</f>
-        <v>4.8029556626481638</v>
+        <v>4.802955662648164</v>
       </c>
       <c r="D22" s="12">
         <f>IF(ISNUMBER(H7),H7,NA())</f>
-        <v>12.824173715651447</v>
+        <v>12.824173715651444</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -3956,7 +4358,7 @@
       </c>
       <c r="C24" s="12">
         <f>IF(ISNUMBER(J6),J6,NA())</f>
-        <v>18.6686364607279</v>
+        <v>18.668636460727903</v>
       </c>
       <c r="D24" s="12">
         <f>IF(ISNUMBER(J7),J7,NA())</f>

--- a/docs/arb_stiffness_old.xlsx
+++ b/docs/arb_stiffness_old.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Parameters" sheetId="5" r:id="rId2"/>
     <sheet name="Samples" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1" calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -587,13 +587,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Soft</c:v>
+                  <c:v>#1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Medium</c:v>
+                  <c:v>#2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Hard</c:v>
+                  <c:v>#3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -602,16 +602,16 @@
             <c:numRef>
               <c:f>Samples!$C$15:$C$17</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.0038661085437566</c:v>
+                  <c:v>4.003866108543757</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.4551008893647595</c:v>
+                  <c:v>8.45510088936476</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.562650598490066</c:v>
+                  <c:v>15.56265059849007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -640,13 +640,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Soft</c:v>
+                  <c:v>#1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Medium</c:v>
+                  <c:v>#2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Hard</c:v>
+                  <c:v>#3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -655,16 +655,16 @@
             <c:numRef>
               <c:f>Samples!$D$15:$D$17</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>11.112357594531263</c:v>
+                  <c:v>11.096327112164879</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.853518344840758</c:v>
+                  <c:v>22.82055028025858</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38.487105034004692</c:v>
+                  <c:v>38.43158424524927</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -864,13 +864,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Soft</c:v>
+                  <c:v>#1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Medium</c:v>
+                  <c:v>#2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Hard</c:v>
+                  <c:v>#3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -879,16 +879,16 @@
             <c:numRef>
               <c:f>Samples!$C$22:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.8029556626481638</c:v>
+                  <c:v>4.802955662648164</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10.142565608820032</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18.6686364607279</c:v>
+                  <c:v>18.668636460727903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -917,13 +917,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Soft</c:v>
+                  <c:v>#1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Medium</c:v>
+                  <c:v>#2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Hard</c:v>
+                  <c:v>#3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -932,16 +932,16 @@
             <c:numRef>
               <c:f>Samples!$D$22:$D$24</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12.824173715651447</c:v>
+                  <c:v>12.805673798881907</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.374015304573856</c:v>
+                  <c:v>26.335968635928243</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44.415896138142486</c:v>
+                  <c:v>44.35182258455383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1392,8 +1392,10 @@
     </row>
     <row r="2" spans="1:15" ht="26.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Astral · ARB H Reference</t>
+        </is>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
@@ -2360,8 +2362,10 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="32" t="s">
-        <v>3</v>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>Astral · ARB H Parameters</t>
+        </is>
       </c>
       <c r="C2" s="32" t="s">
         <v>3</v>
@@ -2479,15 +2483,17 @@
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>10</v>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="D7" s="19">
         <v>14.6</v>
       </c>
       <c r="E7" s="21">
         <f>$E$8*(D7/$D$8)^4</f>
-        <v>941.40636852684645</v>
+        <v>941.4063685268464</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -2500,8 +2506,10 @@
       <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>11</v>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="D8" s="19">
         <v>17.600000000000001</v>
@@ -2520,15 +2528,17 @@
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>12</v>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="D9" s="19">
         <v>20.5</v>
       </c>
       <c r="E9" s="21">
         <f>$E$8*(D9/$D$8)^4</f>
-        <v>3659.1579207191098</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -2541,15 +2551,17 @@
       <c r="B10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>10</v>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="D10" s="19">
         <v>16.2</v>
       </c>
       <c r="E10" s="22">
-        <f>$E$11*(D10/$D$11)^4</f>
-        <v>1429.0674406245323</v>
+        <f>$E$8*(D10/$D$8)^4</f>
+        <v>1427.0058942593776</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -2562,14 +2574,17 @@
       <c r="B11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>11</v>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="D11" s="19">
         <v>19.399999999999999</v>
       </c>
-      <c r="E11" s="20">
-        <v>2939</v>
+      <c r="E11" s="21">
+        <f>$E$8*(D11/$D$8)^4</f>
+        <v>2934.760252738988</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -2582,15 +2597,17 @@
       <c r="B12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>12</v>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="D12" s="19">
         <v>22.1</v>
       </c>
       <c r="E12" s="22">
-        <f>$E$11*(D12/$D$11)^4</f>
-        <v>4949.5049290944507</v>
+        <f>$E$8*(D12/$D$8)^4</f>
+        <v>4942.364864458013</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -2711,7 +2728,7 @@
       </c>
       <c r="G17" s="24">
         <f>IF(COUNT(C17:F17)&lt;4,"",IF(H17=0,"无效半径",IF(D17&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-C17)*1000/H17))))))</f>
-        <v>3.5322945838909319</v>
+        <v>3.532294583890938</v>
       </c>
       <c r="H17" s="26">
         <f>IF(COUNT(C17:F17)&lt;4,"",1000*SQRT((C17-E17)^2+(D17-F17)^2))</f>
@@ -2836,8 +2853,10 @@
       <c r="C23" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>20</v>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E23" s="19">
         <v>167</v>
@@ -2850,7 +2869,7 @@
       </c>
       <c r="H23" s="24">
         <f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",IF(I23=0,"无效半径",IF(G23&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F23)*1000/I23))))))</f>
-        <v>25.144785630678921</v>
+        <v>25.144785630678925</v>
       </c>
       <c r="I23" s="26">
         <f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",1000*SQRT((F23-E17)^2+(G23-F17)^2))</f>
@@ -2866,8 +2885,10 @@
       <c r="C24" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="18" t="s">
-        <v>20</v>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E24" s="19">
         <v>166</v>
@@ -2880,11 +2901,11 @@
       </c>
       <c r="H24" s="25">
         <f>IF(COUNT(F24:G24,E18:F18)&lt;4,"",IF(I24=0,"无效半径",IF(G24&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F24)*1000/I24))))))</f>
-        <v>-0.74405920288851057</v>
+        <v>-0.7440592028885111</v>
       </c>
       <c r="I24" s="27">
         <f>IF(COUNT(F24:G24,E18:F18)&lt;4,"",1000*SQRT((F24-E18)^2+(G24-F18)^2))</f>
-        <v>154.01298646542779</v>
+        <v>154.0129864654278</v>
       </c>
       <c r="J24" s="15"/>
     </row>
@@ -2896,8 +2917,10 @@
       <c r="C25" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>20</v>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E25" s="19">
         <v>266</v>
@@ -2926,8 +2949,10 @@
       <c r="C26" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>20</v>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E26" s="19">
         <v>268</v>
@@ -2940,7 +2965,7 @@
       </c>
       <c r="H26" s="25">
         <f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",IF(I26=0,"无效半径",IF(G26&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F26)*1000/I26))))))</f>
-        <v>13.582963529836702</v>
+        <v>13.582963529836704</v>
       </c>
       <c r="I26" s="27">
         <f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",1000*SQRT((F26-E18)^2+(G26-F18)^2))</f>
@@ -3042,8 +3067,10 @@
       <c r="C32" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>20</v>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E32" s="27">
         <v>46</v>
@@ -3064,8 +3091,10 @@
       <c r="C33" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>20</v>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E33" s="26">
         <v>54</v>
@@ -3086,8 +3115,10 @@
       <c r="C34" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="18" t="s">
-        <v>20</v>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E34" s="27">
         <v>83</v>
@@ -3108,8 +3139,10 @@
       <c r="C35" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>20</v>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E35" s="26">
         <v>111</v>
@@ -3640,14 +3673,23 @@
       <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>28</v>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>#1
+(N/mm)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>#2
+(N/mm)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>#3
+(N/mm)</t>
+        </is>
       </c>
       <c r="K5" s="2" t="s">
         <v>29</v>
@@ -3663,8 +3705,10 @@
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>20</v>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E6" s="7">
         <f>IF(ISNUMBER(Parameters!E23),Parameters!E23,"")</f>
@@ -3676,11 +3720,11 @@
       </c>
       <c r="G6" s="11">
         <f>IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
-        <v>2.2587372953547687E-3</v>
+        <v>0.0022587372953547687</v>
       </c>
       <c r="H6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E7*G6^2,"")</f>
-        <v>4.8029556626481638</v>
+        <v>4.802955662648164</v>
       </c>
       <c r="I6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E8*G6^2,"")</f>
@@ -3688,7 +3732,7 @@
       </c>
       <c r="J6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E9*G6^2,"")</f>
-        <v>18.6686364607279</v>
+        <v>18.668636460727903</v>
       </c>
       <c r="K6" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:F17,Parameters!F23:G23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"无效半径",""))))</f>
@@ -3705,8 +3749,10 @@
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E7" s="8">
         <f>IF(ISNUMBER(Parameters!E24),Parameters!E24,"")</f>
@@ -3718,19 +3764,19 @@
       </c>
       <c r="G7" s="12">
         <f>IF(COUNT(E7:F7)&lt;2,"",IF(E7&lt;=0,"",RADIANS(F7)/E7))</f>
-        <v>2.9956311221279912E-3</v>
+        <v>0.002995631122127991</v>
       </c>
       <c r="H7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E10*G7^2,"")</f>
-        <v>12.824173715651447</v>
+        <v>12.805673798881907</v>
       </c>
       <c r="I7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E11*G7^2,"")</f>
-        <v>26.374015304573856</v>
+        <v>26.335968635928243</v>
       </c>
       <c r="J7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E12*G7^2,"")</f>
-        <v>44.415896138142486</v>
+        <v>44.35182258455383</v>
       </c>
       <c r="K7" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:F18,Parameters!F24:G24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H24)&lt;2,"无效半径",""))))</f>
@@ -3747,8 +3793,10 @@
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>20</v>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E8" s="7">
         <f>IF(ISNUMBER(Parameters!E25),Parameters!E25,"")</f>
@@ -3760,19 +3808,19 @@
       </c>
       <c r="G8" s="11">
         <f>IF(COUNT(E8:F8)&lt;2,"",IF(E8&lt;=0,"",RADIANS(F8)/E8))</f>
-        <v>2.062296985845966E-3</v>
+        <v>0.002062296985845966</v>
       </c>
       <c r="H8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E7*G8^2,"")</f>
-        <v>4.0038661085437566</v>
+        <v>4.003866108543757</v>
       </c>
       <c r="I8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E8*G8^2,"")</f>
-        <v>8.4551008893647595</v>
+        <v>8.45510088936476</v>
       </c>
       <c r="J8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E9*G8^2,"")</f>
-        <v>15.562650598490066</v>
+        <v>15.56265059849007</v>
       </c>
       <c r="K8" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:F17,Parameters!F25:G25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"无效半径",""))))</f>
@@ -3789,8 +3837,10 @@
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E9" s="8">
         <f>IF(ISNUMBER(Parameters!E26),Parameters!E26,"")</f>
@@ -3802,19 +3852,19 @@
       </c>
       <c r="G9" s="12">
         <f>IF(COUNT(E9:F9)&lt;2,"",IF(E9&lt;=0,"",RADIANS(F9)/E9))</f>
-        <v>2.7885391230126001E-3</v>
+        <v>0.0027885391230126</v>
       </c>
       <c r="H9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E10*G9^2,"")</f>
-        <v>11.112357594531263</v>
+        <v>11.096327112164879</v>
       </c>
       <c r="I9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E11*G9^2,"")</f>
-        <v>22.853518344840758</v>
+        <v>22.82055028025858</v>
       </c>
       <c r="J9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E12*G9^2,"")</f>
-        <v>38.487105034004692</v>
+        <v>38.43158424524927</v>
       </c>
       <c r="K9" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:F18,Parameters!F26:G26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"无效半径",""))))</f>
@@ -3906,16 +3956,18 @@
     </row>
     <row r="15" spans="1:13" ht="26.1" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="C15" s="6">
         <f>IF(ISNUMBER(H8),H8,NA())</f>
-        <v>4.0038661085437566</v>
+        <v>4.003866108543757</v>
       </c>
       <c r="D15" s="6">
         <f>IF(ISNUMBER(H9),H9,NA())</f>
-        <v>11.112357594531263</v>
+        <v>11.096327112164879</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -3929,16 +3981,18 @@
     </row>
     <row r="16" spans="1:13" ht="26.1" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4" t="s">
-        <v>11</v>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="C16" s="5">
         <f>IF(ISNUMBER(I8),I8,NA())</f>
-        <v>8.4551008893647595</v>
+        <v>8.45510088936476</v>
       </c>
       <c r="D16" s="5">
         <f>IF(ISNUMBER(I9),I9,NA())</f>
-        <v>22.853518344840758</v>
+        <v>22.82055028025858</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -3952,16 +4006,18 @@
     </row>
     <row r="17" spans="1:13" ht="26.1" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="3" t="s">
-        <v>12</v>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="C17" s="6">
         <f>IF(ISNUMBER(J8),J8,NA())</f>
-        <v>15.562650598490066</v>
+        <v>15.56265059849007</v>
       </c>
       <c r="D17" s="6">
         <f>IF(ISNUMBER(J9),J9,NA())</f>
-        <v>38.487105034004692</v>
+        <v>38.43158424524927</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -4041,16 +4097,18 @@
     </row>
     <row r="22" spans="1:13" ht="26.1" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="4" t="s">
-        <v>10</v>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="C22" s="5">
         <f>IF(ISNUMBER(H6),H6,NA())</f>
-        <v>4.8029556626481638</v>
+        <v>4.802955662648164</v>
       </c>
       <c r="D22" s="5">
         <f>IF(ISNUMBER(H7),H7,NA())</f>
-        <v>12.824173715651447</v>
+        <v>12.805673798881907</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -4064,8 +4122,10 @@
     </row>
     <row r="23" spans="1:13" ht="26.1" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="C23" s="6">
         <f>IF(ISNUMBER(I6),I6,NA())</f>
@@ -4073,7 +4133,7 @@
       </c>
       <c r="D23" s="6">
         <f>IF(ISNUMBER(I7),I7,NA())</f>
-        <v>26.374015304573856</v>
+        <v>26.335968635928243</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -4087,16 +4147,18 @@
     </row>
     <row r="24" spans="1:13" ht="26.1" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="4" t="s">
-        <v>12</v>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="C24" s="5">
         <f>IF(ISNUMBER(J6),J6,NA())</f>
-        <v>18.6686364607279</v>
+        <v>18.668636460727903</v>
       </c>
       <c r="D24" s="5">
         <f>IF(ISNUMBER(J7),J7,NA())</f>
-        <v>44.415896138142486</v>
+        <v>44.35182258455383</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>

--- a/docs/arb_stiffness_old.xlsx
+++ b/docs/arb_stiffness_old.xlsx
@@ -10,14 +10,14 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F30B539-2351-4963-91B0-339964238BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="5" r:id="rId2"/>
     <sheet name="Samples" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="54">
   <si>
     <t>Astral · ARB Outer Reference</t>
   </si>
@@ -69,15 +69,6 @@
     <t>Front</t>
   </si>
   <si>
-    <t>Soft</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Hard</t>
-  </si>
-  <si>
     <t>Rear</t>
   </si>
   <si>
@@ -97,9 +88,6 @@
   </si>
   <si>
     <t>Tarmac</t>
-  </si>
-  <si>
-    <t>Outer</t>
   </si>
   <si>
     <t>Gravel</t>
@@ -120,18 +108,6 @@
 (rad/mm)</t>
   </si>
   <si>
-    <t>Soft
-(N/mm)</t>
-  </si>
-  <si>
-    <t>Medium
-(N/mm)</t>
-  </si>
-  <si>
-    <t>Hard
-(N/mm)</t>
-  </si>
-  <si>
     <t>Input</t>
   </si>
   <si>
@@ -208,6 +184,36 @@
   <si>
     <t>End angle
 (°)</t>
+  </si>
+  <si>
+    <t>Astral · ARB H Parameters</t>
+  </si>
+  <si>
+    <t>#1</t>
+  </si>
+  <si>
+    <t>#2</t>
+  </si>
+  <si>
+    <t>#3</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Astral · ARB H Reference</t>
+  </si>
+  <si>
+    <t>#1
+(N/mm)</t>
+  </si>
+  <si>
+    <t>#2
+(N/mm)</t>
+  </si>
+  <si>
+    <t>#3
+(N/mm)</t>
   </si>
 </sst>
 </file>
@@ -411,11 +417,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -498,15 +504,6 @@
     <xf numFmtId="176" fontId="8" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -517,6 +514,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -602,16 +611,16 @@
             <c:numRef>
               <c:f>Samples!$C$15:$C$17</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.003866108543757</c:v>
+                  <c:v>4.0038661085437566</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.45510088936476</c:v>
+                  <c:v>8.4551008893647595</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.56265059849007</c:v>
+                  <c:v>15.562650598490066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -655,16 +664,16 @@
             <c:numRef>
               <c:f>Samples!$D$15:$D$17</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>11.096327112164879</c:v>
+                  <c:v>11.096327112164881</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>22.82055028025858</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38.43158424524927</c:v>
+                  <c:v>38.431584245249276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -879,16 +888,16 @@
             <c:numRef>
               <c:f>Samples!$C$22:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.802955662648164</c:v>
+                  <c:v>4.8029556626481638</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10.142565608820032</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18.668636460727903</c:v>
+                  <c:v>18.6686364607279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -932,16 +941,16 @@
             <c:numRef>
               <c:f>Samples!$D$22:$D$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12.805673798881907</c:v>
+                  <c:v>12.805673798881909</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>26.335968635928243</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44.35182258455383</c:v>
+                  <c:v>44.351822584553837</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1392,153 +1401,151 @@
     </row>
     <row r="2" spans="1:15" ht="26.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Astral · ARB H Reference</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="32" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="26.1" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="32" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="26.1" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="33" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" ht="26.1" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="30" t="str">
+      <c r="B5" s="34" t="str">
         <f>IF(COUNT(Samples!H6:J9)=0,"待补节点坐标；暂无刚度结果。","")</f>
         <v/>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="26.1" customHeight="1">
@@ -2274,43 +2281,43 @@
     </row>
     <row r="49" spans="1:15" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="30" t="s">
+      <c r="B49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="30" t="s">
+      <c r="D49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="30" t="s">
+      <c r="E49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="F49" s="30" t="s">
+      <c r="F49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="30" t="s">
+      <c r="G49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="30" t="s">
+      <c r="H49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="I49" s="30" t="s">
+      <c r="I49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="30" t="s">
+      <c r="J49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="K49" s="30" t="s">
+      <c r="K49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="30" t="s">
+      <c r="L49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="30" t="s">
+      <c r="M49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="N49" s="30" t="s">
+      <c r="N49" s="34" t="s">
         <v>2</v>
       </c>
       <c r="O49" s="1"/>
@@ -2362,86 +2369,84 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="32" t="inlineStr">
-        <is>
-          <t>Astral · ARB H Parameters</t>
-        </is>
-      </c>
-      <c r="C2" s="32" t="s">
+      <c r="B2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="29" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="15"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="29" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
       <c r="A4" s="15"/>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="30" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="15"/>
@@ -2483,17 +2488,15 @@
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+      <c r="C7" s="17" t="s">
+        <v>46</v>
       </c>
       <c r="D7" s="19">
         <v>14.6</v>
       </c>
       <c r="E7" s="21">
         <f>$E$8*(D7/$D$8)^4</f>
-        <v>941.4063685268464</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -2506,10 +2509,8 @@
       <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+      <c r="C8" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="D8" s="19">
         <v>17.600000000000001</v>
@@ -2528,17 +2529,15 @@
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+      <c r="C9" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="D9" s="19">
         <v>20.5</v>
       </c>
       <c r="E9" s="21">
         <f>$E$8*(D9/$D$8)^4</f>
-        <v>3659.1579207191103</v>
+        <v>3659.1579207191098</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -2549,19 +2548,17 @@
     <row r="10" spans="1:10" ht="27" customHeight="1">
       <c r="A10" s="15"/>
       <c r="B10" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="D10" s="19">
         <v>16.2</v>
       </c>
       <c r="E10" s="22">
         <f>$E$8*(D10/$D$8)^4</f>
-        <v>1427.0058942593776</v>
+        <v>1427.0058942593778</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -2572,19 +2569,17 @@
     <row r="11" spans="1:10" ht="27" customHeight="1">
       <c r="A11" s="15"/>
       <c r="B11" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>47</v>
       </c>
       <c r="D11" s="19">
         <v>19.399999999999999</v>
       </c>
       <c r="E11" s="21">
         <f>$E$8*(D11/$D$8)^4</f>
-        <v>2934.760252738988</v>
+        <v>2934.7602527389881</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -2595,19 +2590,17 @@
     <row r="12" spans="1:10" ht="27" customHeight="1">
       <c r="A12" s="15"/>
       <c r="B12" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="D12" s="19">
         <v>22.1</v>
       </c>
       <c r="E12" s="22">
         <f>$E$8*(D12/$D$8)^4</f>
-        <v>4942.364864458013</v>
+        <v>4942.3648644580135</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -2629,57 +2622,57 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>40</v>
+      <c r="B14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>33</v>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>41</v>
+      <c r="B15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>34</v>
       </c>
       <c r="J15" s="15"/>
     </row>
@@ -2689,22 +2682,22 @@
         <v>5</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
@@ -2728,7 +2721,7 @@
       </c>
       <c r="G17" s="24">
         <f>IF(COUNT(C17:F17)&lt;4,"",IF(H17=0,"无效半径",IF(D17&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-C17)*1000/H17))))))</f>
-        <v>3.532294583890938</v>
+        <v>3.5322945838909319</v>
       </c>
       <c r="H17" s="26">
         <f>IF(COUNT(C17:F17)&lt;4,"",1000*SQRT((C17-E17)^2+(D17-F17)^2))</f>
@@ -2740,7 +2733,7 @@
     <row r="18" spans="1:10" ht="27" customHeight="1">
       <c r="A18" s="15"/>
       <c r="B18" s="18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="23">
         <v>1.321</v>
@@ -2779,29 +2772,29 @@
     </row>
     <row r="20" spans="1:10" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="I20" s="31" t="s">
-        <v>48</v>
+      <c r="B20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>41</v>
       </c>
       <c r="J20" s="15"/>
     </row>
@@ -2820,43 +2813,41 @@
     <row r="22" spans="1:10" ht="42" customHeight="1">
       <c r="A22" s="15"/>
       <c r="B22" s="16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:10" ht="27" customHeight="1">
       <c r="A23" s="15"/>
       <c r="B23" s="17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D23" s="17" t="s">
+        <v>49</v>
       </c>
       <c r="E23" s="19">
         <v>167</v>
@@ -2869,7 +2860,7 @@
       </c>
       <c r="H23" s="24">
         <f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",IF(I23=0,"无效半径",IF(G23&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F23)*1000/I23))))))</f>
-        <v>25.144785630678925</v>
+        <v>25.144785630678921</v>
       </c>
       <c r="I23" s="26">
         <f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",1000*SQRT((F23-E17)^2+(G23-F17)^2))</f>
@@ -2880,15 +2871,13 @@
     <row r="24" spans="1:10" ht="27" customHeight="1">
       <c r="A24" s="15"/>
       <c r="B24" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E24" s="19">
         <v>166</v>
@@ -2901,26 +2890,24 @@
       </c>
       <c r="H24" s="25">
         <f>IF(COUNT(F24:G24,E18:F18)&lt;4,"",IF(I24=0,"无效半径",IF(G24&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F24)*1000/I24))))))</f>
-        <v>-0.7440592028885111</v>
+        <v>-0.74405920288851057</v>
       </c>
       <c r="I24" s="27">
         <f>IF(COUNT(F24:G24,E18:F18)&lt;4,"",1000*SQRT((F24-E18)^2+(G24-F18)^2))</f>
-        <v>154.0129864654278</v>
+        <v>154.01298646542779</v>
       </c>
       <c r="J24" s="15"/>
     </row>
     <row r="25" spans="1:10" ht="27" customHeight="1">
       <c r="A25" s="15"/>
       <c r="B25" s="17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D25" s="17" t="s">
+        <v>49</v>
       </c>
       <c r="E25" s="19">
         <v>266</v>
@@ -2944,15 +2931,13 @@
     <row r="26" spans="1:10" ht="27" customHeight="1">
       <c r="A26" s="15"/>
       <c r="B26" s="18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E26" s="19">
         <v>268</v>
@@ -2965,7 +2950,7 @@
       </c>
       <c r="H26" s="25">
         <f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",IF(I26=0,"无效半径",IF(G26&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F26)*1000/I26))))))</f>
-        <v>13.582963529836704</v>
+        <v>13.582963529836702</v>
       </c>
       <c r="I26" s="27">
         <f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",1000*SQRT((F26-E18)^2+(G26-F18)^2))</f>
@@ -3011,48 +2996,48 @@
     </row>
     <row r="30" spans="1:10" ht="27" customHeight="1">
       <c r="A30" s="15"/>
-      <c r="B30" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="31" t="s">
-        <v>14</v>
+      <c r="B30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>11</v>
       </c>
       <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1">
       <c r="A31" s="15"/>
       <c r="B31" s="16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
@@ -3062,15 +3047,13 @@
     <row r="32" spans="1:10" ht="27" customHeight="1">
       <c r="A32" s="15"/>
       <c r="B32" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D32" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E32" s="27">
         <v>46</v>
@@ -3086,15 +3069,13 @@
     <row r="33" spans="1:10" ht="27" customHeight="1">
       <c r="A33" s="15"/>
       <c r="B33" s="17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>49</v>
       </c>
       <c r="E33" s="26">
         <v>54</v>
@@ -3110,15 +3091,13 @@
     <row r="34" spans="1:10" ht="27" customHeight="1">
       <c r="A34" s="15"/>
       <c r="B34" s="18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D34" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E34" s="27">
         <v>83</v>
@@ -3134,15 +3113,13 @@
     <row r="35" spans="1:10" ht="27" customHeight="1">
       <c r="A35" s="15"/>
       <c r="B35" s="17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>49</v>
       </c>
       <c r="E35" s="26">
         <v>111</v>
@@ -3570,70 +3547,70 @@
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>22</v>
+      <c r="B2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="26.1" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
+      <c r="B3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -3656,43 +3633,34 @@
     <row r="5" spans="1:13" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>#1
-(N/mm)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>#2
-(N/mm)</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>#3
-(N/mm)</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -3700,15 +3668,13 @@
     <row r="6" spans="1:13" ht="26.1" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E6" s="7">
         <f>IF(ISNUMBER(Parameters!E23),Parameters!E23,"")</f>
@@ -3720,11 +3686,11 @@
       </c>
       <c r="G6" s="11">
         <f>IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
-        <v>0.0022587372953547687</v>
+        <v>2.2587372953547687E-3</v>
       </c>
       <c r="H6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E7*G6^2,"")</f>
-        <v>4.802955662648164</v>
+        <v>4.8029556626481638</v>
       </c>
       <c r="I6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E8*G6^2,"")</f>
@@ -3732,7 +3698,7 @@
       </c>
       <c r="J6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E9*G6^2,"")</f>
-        <v>18.668636460727903</v>
+        <v>18.6686364607279</v>
       </c>
       <c r="K6" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:F17,Parameters!F23:G23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"无效半径",""))))</f>
@@ -3744,15 +3710,13 @@
     <row r="7" spans="1:13" ht="26.1" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E7" s="8">
         <f>IF(ISNUMBER(Parameters!E24),Parameters!E24,"")</f>
@@ -3764,11 +3728,11 @@
       </c>
       <c r="G7" s="12">
         <f>IF(COUNT(E7:F7)&lt;2,"",IF(E7&lt;=0,"",RADIANS(F7)/E7))</f>
-        <v>0.002995631122127991</v>
+        <v>2.9956311221279912E-3</v>
       </c>
       <c r="H7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E10*G7^2,"")</f>
-        <v>12.805673798881907</v>
+        <v>12.805673798881909</v>
       </c>
       <c r="I7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E11*G7^2,"")</f>
@@ -3776,7 +3740,7 @@
       </c>
       <c r="J7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E12*G7^2,"")</f>
-        <v>44.35182258455383</v>
+        <v>44.351822584553837</v>
       </c>
       <c r="K7" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:F18,Parameters!F24:G24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H24)&lt;2,"无效半径",""))))</f>
@@ -3788,15 +3752,13 @@
     <row r="8" spans="1:13" ht="26.1" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E8" s="7">
         <f>IF(ISNUMBER(Parameters!E25),Parameters!E25,"")</f>
@@ -3808,19 +3770,19 @@
       </c>
       <c r="G8" s="11">
         <f>IF(COUNT(E8:F8)&lt;2,"",IF(E8&lt;=0,"",RADIANS(F8)/E8))</f>
-        <v>0.002062296985845966</v>
+        <v>2.062296985845966E-3</v>
       </c>
       <c r="H8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E7*G8^2,"")</f>
-        <v>4.003866108543757</v>
+        <v>4.0038661085437566</v>
       </c>
       <c r="I8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E8*G8^2,"")</f>
-        <v>8.45510088936476</v>
+        <v>8.4551008893647595</v>
       </c>
       <c r="J8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E9*G8^2,"")</f>
-        <v>15.56265059849007</v>
+        <v>15.562650598490066</v>
       </c>
       <c r="K8" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:F17,Parameters!F25:G25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"无效半径",""))))</f>
@@ -3832,15 +3794,13 @@
     <row r="9" spans="1:13" ht="26.1" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E9" s="8">
         <f>IF(ISNUMBER(Parameters!E26),Parameters!E26,"")</f>
@@ -3852,11 +3812,11 @@
       </c>
       <c r="G9" s="12">
         <f>IF(COUNT(E9:F9)&lt;2,"",IF(E9&lt;=0,"",RADIANS(F9)/E9))</f>
-        <v>0.0027885391230126</v>
+        <v>2.7885391230126001E-3</v>
       </c>
       <c r="H9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E10*G9^2,"")</f>
-        <v>11.096327112164879</v>
+        <v>11.096327112164881</v>
       </c>
       <c r="I9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E11*G9^2,"")</f>
@@ -3864,7 +3824,7 @@
       </c>
       <c r="J9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E12*G9^2,"")</f>
-        <v>38.43158424524927</v>
+        <v>38.431584245249276</v>
       </c>
       <c r="K9" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:F18,Parameters!F26:G26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"无效半径",""))))</f>
@@ -3936,13 +3896,13 @@
     <row r="14" spans="1:13" ht="39.950000000000003" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -3956,18 +3916,16 @@
     </row>
     <row r="15" spans="1:13" ht="26.1" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+      <c r="B15" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C15" s="6">
         <f>IF(ISNUMBER(H8),H8,NA())</f>
-        <v>4.003866108543757</v>
+        <v>4.0038661085437566</v>
       </c>
       <c r="D15" s="6">
         <f>IF(ISNUMBER(H9),H9,NA())</f>
-        <v>11.096327112164879</v>
+        <v>11.096327112164881</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -3981,14 +3939,12 @@
     </row>
     <row r="16" spans="1:13" ht="26.1" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+      <c r="B16" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="C16" s="5">
         <f>IF(ISNUMBER(I8),I8,NA())</f>
-        <v>8.45510088936476</v>
+        <v>8.4551008893647595</v>
       </c>
       <c r="D16" s="5">
         <f>IF(ISNUMBER(I9),I9,NA())</f>
@@ -4006,18 +3962,16 @@
     </row>
     <row r="17" spans="1:13" ht="26.1" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+      <c r="B17" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C17" s="6">
         <f>IF(ISNUMBER(J8),J8,NA())</f>
-        <v>15.56265059849007</v>
+        <v>15.562650598490066</v>
       </c>
       <c r="D17" s="6">
         <f>IF(ISNUMBER(J9),J9,NA())</f>
-        <v>38.43158424524927</v>
+        <v>38.431584245249276</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -4077,13 +4031,13 @@
     <row r="21" spans="1:13" ht="39.950000000000003" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -4097,18 +4051,16 @@
     </row>
     <row r="22" spans="1:13" ht="26.1" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+      <c r="B22" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C22" s="5">
         <f>IF(ISNUMBER(H6),H6,NA())</f>
-        <v>4.802955662648164</v>
+        <v>4.8029556626481638</v>
       </c>
       <c r="D22" s="5">
         <f>IF(ISNUMBER(H7),H7,NA())</f>
-        <v>12.805673798881907</v>
+        <v>12.805673798881909</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -4122,10 +4074,8 @@
     </row>
     <row r="23" spans="1:13" ht="26.1" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+      <c r="B23" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C23" s="6">
         <f>IF(ISNUMBER(I6),I6,NA())</f>
@@ -4147,18 +4097,16 @@
     </row>
     <row r="24" spans="1:13" ht="26.1" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+      <c r="B24" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C24" s="5">
         <f>IF(ISNUMBER(J6),J6,NA())</f>
-        <v>18.668636460727903</v>
+        <v>18.6686364607279</v>
       </c>
       <c r="D24" s="5">
         <f>IF(ISNUMBER(J7),J7,NA())</f>
-        <v>44.35182258455383</v>
+        <v>44.351822584553837</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -4232,14 +4180,14 @@
     </row>
     <row r="29" spans="1:13" ht="26.1" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>31</v>
+      <c r="B29" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>24</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -4254,7 +4202,7 @@
     <row r="30" spans="1:13" ht="26.1" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C30" s="1">
         <v>223</v>
@@ -4273,7 +4221,7 @@
     <row r="31" spans="1:13" ht="26.1" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C31" s="1">
         <v>267</v>
@@ -4292,7 +4240,7 @@
     <row r="32" spans="1:13" ht="26.1" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1">
         <v>236</v>
@@ -4311,7 +4259,7 @@
     <row r="33" spans="1:13" ht="26.1" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C33" s="1">
         <v>238</v>
@@ -4330,7 +4278,7 @@
     <row r="34" spans="1:13" ht="26.1" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C34" s="1">
         <v>279</v>
@@ -4349,7 +4297,7 @@
     <row r="35" spans="1:13" ht="26.1" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C35" s="1">
         <v>16</v>
@@ -4368,7 +4316,7 @@
     <row r="36" spans="1:13" ht="26.1" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1">
         <v>23</v>
@@ -4387,7 +4335,7 @@
     <row r="37" spans="1:13" ht="26.1" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C37" s="1">
         <v>24</v>
